--- a/data/age.xlsx
+++ b/data/age.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\dbb\Qalabs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28E2A747-578C-4FD4-8A8B-F6B6401DEA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE336ED-23C7-4617-959B-89B1C3915B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1CCBBDC9-4DB6-4838-AF56-B93D1C8B6C8E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1CCBBDC9-4DB6-4838-AF56-B93D1C8B6C8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,26 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>age</t>
   </si>
   <si>
     <t>23 yr</t>
+  </si>
+  <si>
+    <t>24 yr</t>
+  </si>
+  <si>
+    <t>25 yr</t>
   </si>
 </sst>
 </file>
@@ -398,17 +395,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E0D623-DD85-4F37-956B-231B07BBD6D0}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/age.xlsx
+++ b/data/age.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\dbb\Qalabs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE336ED-23C7-4617-959B-89B1C3915B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0581D1EA-BE44-4AB5-A5FF-06814FED2EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1CCBBDC9-4DB6-4838-AF56-B93D1C8B6C8E}"/>
   </bookViews>
@@ -395,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E0D623-DD85-4F37-956B-231B07BBD6D0}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -418,6 +418,11 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
